--- a/social_worker_forms/008_free_local_assistance_request_form--social_worker_forms.xlsx
+++ b/social_worker_forms/008_free_local_assistance_request_form--social_worker_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'assistance_with_food',_'value':_'assistance_with_food'}</t>
+          <t>assistance_with_food</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Assistance with Food', 'value': 'assistance_with_food'}</t>
+          <t>Assistance with Food</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'emergency_assistance',_'value':_'emergency_assistance'}</t>
+          <t>emergency_assistance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Emergency Assistance', 'value': 'emergency_assistance'}</t>
+          <t>Emergency Assistance</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Phone', 'value': 'phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in_person',_'value':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In Person', 'value': 'in_person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cash',_'value':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cash', 'value': 'cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'credit',_'value':_'credit'}</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Credit', 'value': 'credit'}</t>
+          <t>Credit</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'open',_'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Open', 'value': 'open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Closed', 'value': 'closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
